--- a/product_selector_out/STM32F303 - diff.xlsx
+++ b/product_selector_out/STM32F303 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,21 +43,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C0C0C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,16 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +601,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1110</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="18">
@@ -667,22 +649,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -694,70 +672,62 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>115 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F303RD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -766,21 +736,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F303ZD</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -789,183 +759,159 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303VD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303K8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>CHANGED</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303VC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303C8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -974,21 +920,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F303RD</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -997,21 +943,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F303VD</t>
+          <t>STM32F303RC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1020,21 +966,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F303VD</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1043,21 +989,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F303K8</t>
+          <t>STM32F303CC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1066,21 +1012,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F303K8</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1089,21 +1035,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F303VC</t>
+          <t>STM32F303CB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1112,21 +1058,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F303VC</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1135,21 +1081,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F303C8</t>
+          <t>STM32F303VE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1158,21 +1104,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F303C8</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1181,21 +1127,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F303RC</t>
+          <t>STM32F303RB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1204,21 +1150,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F303RC</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1227,21 +1173,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F303CC</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1250,21 +1196,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F303CC</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1273,21 +1219,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F303CB</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1296,21 +1242,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F303CB</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1319,21 +1265,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F303VE</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1342,21 +1288,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F303VE</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1365,21 +1311,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F303RB</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1388,21 +1334,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F303RB</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1411,21 +1357,21 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F303R6</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1434,21 +1380,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F303R6</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1457,21 +1403,21 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F303RE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1480,21 +1426,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1503,478 +1449,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F303R8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32F303K6</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32F303C6</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32F303C6</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>115 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32F303ZE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>51 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STM32F303RE</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STM32F303R8</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32F303R8</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E72"/>
+  <autoFilter ref="A18:E54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F303 - diff.xlsx
+++ b/product_selector_out/STM32F303 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,13 +86,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -531,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -601,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -611,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1116</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="18">
@@ -1155,18 +1179,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1178,71 +1206,83 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F303VB</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1265,7 +1305,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F303K6</t>
+          <t>STM32F303R6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1288,7 +1328,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F303C6</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1311,7 +1351,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F303C6</t>
+          <t>STM32F303VB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1334,7 +1374,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F303ZE</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1357,7 +1397,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F303ZE</t>
+          <t>STM32F303K6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1380,7 +1420,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F303RE</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1403,7 +1443,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F303RE</t>
+          <t>STM32F303C6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1426,7 +1466,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F303R8</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1449,7 +1489,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F303R8</t>
+          <t>STM32F303ZE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1469,8 +1509,208 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32F303RE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32F303RE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32F303R8</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32F303R8</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32F303R8</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>7 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32F303R8</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32F303R8</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32F303R8</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E54"/>
+  <autoFilter ref="A18:E62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F303 - diff.xlsx
+++ b/product_selector_out/STM32F303 - diff.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1152</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1112</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="18">
